--- a/frontend/public/sample-30-blocks.xlsx
+++ b/frontend/public/sample-30-blocks.xlsx
@@ -397,12 +397,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:E31"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" customWidth="1"/>
     <col min="3" max="3" width="14.83203125" customWidth="1"/>
     <col min="4" max="4" width="14.83203125" customWidth="1"/>
+    <col min="5" max="5" width="14.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -418,6 +419,9 @@
       <c r="D1" t="str">
         <v>자재준비 여부</v>
       </c>
+      <c r="E1" t="str">
+        <v>자재 납기일</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -432,6 +436,9 @@
       <c r="D2" t="str">
         <v>준비</v>
       </c>
+      <c r="E2" t="str">
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -446,6 +453,9 @@
       <c r="D3" t="str">
         <v>준비</v>
       </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -460,6 +470,9 @@
       <c r="D4" t="str">
         <v>미준비</v>
       </c>
+      <c r="E4">
+        <v>4</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -474,6 +487,9 @@
       <c r="D5" t="str">
         <v>준비</v>
       </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
@@ -488,6 +504,9 @@
       <c r="D6" t="str">
         <v>준비</v>
       </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
@@ -502,6 +521,9 @@
       <c r="D7" t="str">
         <v>준비</v>
       </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
@@ -516,6 +538,9 @@
       <c r="D8" t="str">
         <v>준비</v>
       </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
@@ -530,6 +555,9 @@
       <c r="D9" t="str">
         <v>미준비</v>
       </c>
+      <c r="E9">
+        <v>4</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
@@ -544,6 +572,9 @@
       <c r="D10" t="str">
         <v>준비</v>
       </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
@@ -558,6 +589,9 @@
       <c r="D11" t="str">
         <v>준비</v>
       </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
@@ -572,6 +606,9 @@
       <c r="D12" t="str">
         <v>준비</v>
       </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
@@ -586,6 +623,9 @@
       <c r="D13" t="str">
         <v>준비</v>
       </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
@@ -600,6 +640,9 @@
       <c r="D14" t="str">
         <v>준비</v>
       </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
@@ -614,6 +657,9 @@
       <c r="D15" t="str">
         <v>준비</v>
       </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
@@ -628,6 +674,9 @@
       <c r="D16" t="str">
         <v>준비</v>
       </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
@@ -642,6 +691,9 @@
       <c r="D17" t="str">
         <v>미준비</v>
       </c>
+      <c r="E17" t="str">
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
@@ -656,6 +708,9 @@
       <c r="D18" t="str">
         <v>미준비</v>
       </c>
+      <c r="E18">
+        <v>4</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
@@ -670,6 +725,9 @@
       <c r="D19" t="str">
         <v>미준비</v>
       </c>
+      <c r="E19" t="str">
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
@@ -684,6 +742,9 @@
       <c r="D20" t="str">
         <v>준비</v>
       </c>
+      <c r="E20" t="str">
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
@@ -698,6 +759,9 @@
       <c r="D21" t="str">
         <v>준비</v>
       </c>
+      <c r="E21" t="str">
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
@@ -712,6 +776,9 @@
       <c r="D22" t="str">
         <v>준비</v>
       </c>
+      <c r="E22" t="str">
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
@@ -726,6 +793,9 @@
       <c r="D23" t="str">
         <v>미준비</v>
       </c>
+      <c r="E23">
+        <v>4</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
@@ -740,6 +810,9 @@
       <c r="D24" t="str">
         <v>준비</v>
       </c>
+      <c r="E24" t="str">
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
@@ -754,6 +827,9 @@
       <c r="D25" t="str">
         <v>준비</v>
       </c>
+      <c r="E25" t="str">
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
@@ -768,6 +844,9 @@
       <c r="D26" t="str">
         <v>미준비</v>
       </c>
+      <c r="E26">
+        <v>2</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
@@ -782,6 +861,9 @@
       <c r="D27" t="str">
         <v>준비</v>
       </c>
+      <c r="E27" t="str">
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
@@ -796,6 +878,9 @@
       <c r="D28" t="str">
         <v>준비</v>
       </c>
+      <c r="E28" t="str">
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
@@ -810,6 +895,9 @@
       <c r="D29" t="str">
         <v>미준비</v>
       </c>
+      <c r="E29" t="str">
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
@@ -824,6 +912,9 @@
       <c r="D30" t="str">
         <v>준비</v>
       </c>
+      <c r="E30" t="str">
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
@@ -838,10 +929,13 @@
       <c r="D31" t="str">
         <v>준비</v>
       </c>
+      <c r="E31" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D31"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E31"/>
   </ignoredErrors>
 </worksheet>
 </file>